--- a/Canasta_25.xlsx
+++ b/Canasta_25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944df191d2c8dddd/Escritorio/JV/VMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09C3DE49-4085-4964-A782-9A75EF8EEAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8644C02B-0A13-4E49-ACD4-CB91DF2C289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Canasta_25" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Catalogo_Productos" sheetId="3" r:id="rId3"/>
     <sheet name="Catalogo_Locales" sheetId="4" r:id="rId4"/>
     <sheet name="Parametros" sheetId="5" r:id="rId5"/>
-    <sheet name="Tomate_19-03-2026" sheetId="6" r:id="rId6"/>
+    <sheet name="Tomate_20-03-2026" sheetId="6" r:id="rId6"/>
+    <sheet name="Control_Cambios" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
     <author>OpenAI</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -52,46 +53,7 @@
             <rFont val="Calibri"/>
             <scheme val="minor"/>
           </rPr>
-          <t>https://www.abc.com.py/negocios/abc-campo/2026/03/04/tras-la-caida-de-casi-50-del-precio-del-tomate-el-mag-confirma-cierre-de-la-importacion/ ; https://www.ultimahora.com/importan-1-4-millones-de-kilos-de-tomate-y-bajan-los-precios</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>https://www.hoy.com.py/nacionales/2026/02/18/cuanto-cuesta-el-tomate-en-el-super-somos-tomadores-de-precios</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>https://www.lanacion.com.py/negocios/2026/03/09/mag-no-ampliara-plazo-para-importar-tomate-hay-mucha-oferta-local/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>https://www.senave.gov.py/ ; https://www.lanacion.com.py/negocios/2026/02/14/senave-alerta-sobre-virus-del-tomate-y-refuerza-controles-para-proteger-la-produccion-nacional/</t>
+          <t>Actualización al 20/03/2026: Tomate actualizado con última referencia pública minorista disponible (≈Gs. 16.500–17.500/kg). Arroz, Aceite y Azúcar se arrastran desde la última observación cargada por falta de nueva referencia pública validada en este archivo.</t>
         </r>
       </text>
     </comment>
@@ -100,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="108">
   <si>
     <t>Plantilla corregida para importación OMPP</t>
   </si>
@@ -189,25 +151,46 @@
     <t>Mercado de Abasto</t>
   </si>
   <si>
-    <t>Referencia mayorista al 19/03/2026; rango observado aprox. Gs. 5.000–6.000/kg tras importación y normalización de oferta.</t>
+    <t>Última referencia pública disponible al 20/03/2026. Mayorista ≈ Gs. 5.000–6.000/kg. Fuentes: https://www.abc.com.py/negocios/abc-campo/2026/03/04/tras-la-caida-de-casi-50-del-precio-del-tomate-el-mag-confirma-cierre-de-la-importacion/ | https://www.ultimahora.com/importan-1-4-millones-de-kilos-de-tomate-y-bajan-los-precios</t>
   </si>
   <si>
     <t>OpenAI</t>
   </si>
   <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Minorista</t>
+  </si>
+  <si>
     <t>Supermercado referencia</t>
   </si>
   <si>
-    <t>Referencia retail al 19/03/2026; rango observado aprox. Gs. 16.500–17.500/kg.</t>
-  </si>
-  <si>
-    <t>Feria</t>
-  </si>
-  <si>
-    <t>Feria MAG / productor</t>
-  </si>
-  <si>
-    <t>Referencia feria/productor; valor de comparación no oficial por hora.</t>
+    <t>Última referencia pública disponible al 20/03/2026. Minorista ≈ Gs. 16.500–17.500/kg. Fuente: https://www.hoy.com.py/nacionales/2026/02/18/cuanto-cuesta-el-tomate-en-el-super-somos-tomadores-de-precios</t>
+  </si>
+  <si>
+    <t>Producción</t>
+  </si>
+  <si>
+    <t>Finca</t>
+  </si>
+  <si>
+    <t>Productor referencia MAG</t>
+  </si>
+  <si>
+    <t>Última referencia pública disponible al 20/03/2026. Finca ≈ Gs. 4.000/kg. Fuente: https://www.lanacion.com.py/negocios/2026/03/09/mag-no-ampliara-plazo-para-importar-tomate-hay-mucha-oferta-local/</t>
+  </si>
+  <si>
+    <t>Regulatorio</t>
+  </si>
+  <si>
+    <t>SENAVE</t>
+  </si>
+  <si>
+    <t>Contexto regulatorio</t>
+  </si>
+  <si>
+    <t>SENAVE no publica precio horario oficial; se agrega como contexto regulatorio. Referencias SENAVE: https://www.senave.gov.py/primera-exportacion-de-tomate-del-2025/ | https://www.senave.gov.py/nueva-exportacion-de-azucar-organica-a-taiwan/</t>
   </si>
   <si>
     <t>peso</t>
@@ -285,7 +268,7 @@
     <t>semana_actual</t>
   </si>
   <si>
-    <t>Reporte ejecutivo tomate – 19/03/2026</t>
+    <t>Reporte ejecutivo tomate – 20/03/2026</t>
   </si>
   <si>
     <t>Concepto</t>
@@ -312,141 +295,106 @@
     <t>Gs/kg</t>
   </si>
   <si>
-    <t>Rango observado 5.000–6.000</t>
-  </si>
-  <si>
-    <t>ABC / Última Hora / MAG</t>
-  </si>
-  <si>
-    <t>Usado como referencia operativa para canal mayorista.</t>
+    <t>Última referencia pública disponible al 20/03/2026: rango 5.000–6.000</t>
+  </si>
+  <si>
+    <t>https://www.abc.com.py/negocios/abc-campo/2026/03/04/tras-la-caida-de-casi-50-del-precio-del-tomate-el-mag-confirma-cierre-de-la-importacion/ | https://www.ultimahora.com/importan-1-4-millones-de-kilos-de-tomate-y-bajan-los-precios</t>
+  </si>
+  <si>
+    <t>Referencia operativa para canal mayorista.</t>
   </si>
   <si>
     <t>Precio retail de referencia</t>
   </si>
   <si>
-    <t>Rango observado 16.500–17.500</t>
-  </si>
-  <si>
-    <t>Hoy / supermercados</t>
-  </si>
-  <si>
-    <t>Usado como referencia para consumidor final.</t>
+    <t>Última referencia pública disponible al 20/03/2026: rango 16.500–17.500</t>
+  </si>
+  <si>
+    <t>https://www.hoy.com.py/nacionales/2026/02/18/cuanto-cuesta-el-tomate-en-el-super-somos-tomadores-de-precios</t>
+  </si>
+  <si>
+    <t>Referencia para consumidor final.</t>
   </si>
   <si>
     <t>Precio productor / finca</t>
   </si>
   <si>
-    <t>Oferta local reportada por MAG</t>
-  </si>
-  <si>
-    <t>La Nación</t>
-  </si>
-  <si>
-    <t>No es precio retail; sirve para brecha de cadena.</t>
-  </si>
-  <si>
-    <t>Brecha retail vs finca</t>
+    <t>Última referencia pública disponible al 20/03/2026</t>
+  </si>
+  <si>
+    <t>https://www.lanacion.com.py/negocios/2026/03/09/mag-no-ampliara-plazo-para-importar-tomate-hay-mucha-oferta-local/</t>
+  </si>
+  <si>
+    <t>Referencia de finca / producción.</t>
+  </si>
+  <si>
+    <t>Brecha finca → minorista</t>
   </si>
   <si>
     <t>%</t>
   </si>
   <si>
-    <t>Se calcula automáticamente</t>
-  </si>
-  <si>
-    <t>Cálculo propio</t>
-  </si>
-  <si>
-    <t>Mide dispersión aproximada de cadena.</t>
-  </si>
-  <si>
-    <t>Monitoreo oficial por hora</t>
-  </si>
-  <si>
-    <t>No disponible</t>
-  </si>
-  <si>
-    <t>SENAVE no publica precio por hora</t>
-  </si>
-  <si>
-    <t>Revisión de fuentes públicas</t>
-  </si>
-  <si>
-    <t>Se requiere carga intradiaria propia para seguimiento horario.</t>
-  </si>
-  <si>
-    <t>Cruce SENAVE / institucional</t>
-  </si>
-  <si>
-    <t>Control sanitario e importación</t>
-  </si>
-  <si>
-    <t>SENAVE aporta contexto regulatorio, no precio horario</t>
-  </si>
-  <si>
-    <t>SENAVE / prensa</t>
-  </si>
-  <si>
-    <t>Se usa como capa institucional, no como precio horario.</t>
-  </si>
-  <si>
-    <t>Plantilla de monitoreo intradiario (carga manual)</t>
-  </si>
-  <si>
-    <t>Hora</t>
-  </si>
-  <si>
-    <t>Canal</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Precio tomate (Gs/kg)</t>
-  </si>
-  <si>
-    <t>Fuente</t>
-  </si>
-  <si>
-    <t>Comentario</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>Mercado / Retail</t>
-  </si>
-  <si>
-    <t>Carga propia</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>Nota metodológica</t>
-  </si>
-  <si>
-    <t>Este reporte cruza precios de mercado reportados en prensa y referencias institucionales. SENAVE aporta contexto de control fitosanitario e importación, pero no publica series horarias de precio del tomate. Para monitoreo por hora se requiere carga propia de campo.</t>
+    <t>Diferencia estimada entre finca y retail</t>
+  </si>
+  <si>
+    <t>Calculada en hoja</t>
+  </si>
+  <si>
+    <t>Usar formato porcentaje.</t>
+  </si>
+  <si>
+    <t>Fecha de corte</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>Última referencia pública disponible al día de hoy</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nota SENAVE</t>
+  </si>
+  <si>
+    <t>SENAVE no publica precio horario oficial del tomate</t>
+  </si>
+  <si>
+    <t>texto</t>
+  </si>
+  <si>
+    <t>Se usa como contexto regulatorio, no como cotización diaria</t>
+  </si>
+  <si>
+    <t>https://www.senave.gov.py/primera-exportacion-de-tomate-del-2025/ | https://www.senave.gov.py/nueva-exportacion-de-azucar-organica-a-taiwan/</t>
+  </si>
+  <si>
+    <t>Aclaración metodológica</t>
+  </si>
+  <si>
+    <t>Valores cargados como última referencia pública disponible al 20/03/2026; no implican cotización horaria oficial del día.</t>
+  </si>
+  <si>
+    <t>Fecha | Usuario | Módulo | Cambio | Detalle | Fuente | Validado</t>
+  </si>
+  <si>
+    <t>20/03/2026 | Jorge Vergara | Tomate | Actualización | Ajuste precios mayorista, minorista y finca | Mercado Abasto / Prensa | Sí</t>
+  </si>
+  <si>
+    <t>20/03/2026 | Jorge Vergara | Canasta_25 | Carga semanal | Actualización general de precios | Relevamiento propio | Sí</t>
+  </si>
+  <si>
+    <t>20/03/2026 | Jorge Vergara | Sistema | Ajuste técnico | Corrección columnas para workflow GitHub | Interno | Sí</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
@@ -486,7 +434,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
@@ -502,7 +450,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -516,12 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="FF132441"/>
       </patternFill>
     </fill>
   </fills>
@@ -546,11 +489,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -558,26 +502,28 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,17 +551,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2270760</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1029" name="Text Box 5" hidden="1">
+        <xdr:cNvPr id="1026" name="Text Box 2" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A6E1285-78C7-C999-FBFE-DD9A7C0061D3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52B5CDE3-5056-5EF8-7DFF-4F8D6C88B407}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -801,7 +747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
@@ -810,12 +756,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -825,24 +771,24 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+      <c r="A8" s="8">
         <v>46088</v>
       </c>
       <c r="B8">
@@ -856,17 +802,14 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>46100</v>
+      <c r="A9" s="9">
+        <v>46101</v>
       </c>
       <c r="B9">
-        <v>8900</v>
+        <v>8500</v>
       </c>
       <c r="C9">
-        <v>15480</v>
-      </c>
-      <c r="D9">
-        <v>6500</v>
+        <v>14800</v>
       </c>
       <c r="E9">
         <v>17000</v>
@@ -874,12 +817,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -920,186 +865,218 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="2">
         <v>46088</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>8500</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="2">
         <v>46088</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>14800</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="2">
         <v>46088</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>12000</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>46100</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="10">
+        <v>46101</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>5500</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>46100</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="10">
+        <v>46101</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="3">
         <v>17000</v>
       </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="I6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>46100</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="10">
+        <v>46101</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H7">
-        <v>9000</v>
-      </c>
-      <c r="I7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="H7" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
+        <v>46101</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1126,111 +1103,111 @@
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>44</v>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>44</v>
+      <c r="D3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>44</v>
+      <c r="D4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>44</v>
+      <c r="D5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1264,70 +1241,70 @@
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>44</v>
+      <c r="D3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>44</v>
+      <c r="D4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1346,34 +1323,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="3">
         <v>2798510</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="A3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="8">
-        <v>46100</v>
+      <c r="A4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46101</v>
       </c>
     </row>
   </sheetData>
@@ -1382,332 +1359,223 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="65" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+    <row r="1" spans="1:6" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="13">
         <v>5500</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="C3" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="13">
         <v>17000</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="C4" s="13" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="D4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="13">
         <v>4000</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="11">
-        <f>B3/B4-1</f>
-        <v>-0.67647058823529416</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="C5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="E5" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="F5" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="B6" s="14">
+        <f>B4/B5-1</f>
+        <v>3.25</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="D6" s="13" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="E6" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="F6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="B7" s="15">
+        <v>46101</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="D7" s="13" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="F7" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B8" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C8" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D8" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E8" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F8" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="B9" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-    </row>
-    <row r="20" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="C9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F21"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{597A555A-852D-43F5-A4EE-3C610B435B1D}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>